--- a/backend/data/financials_by_company/0176.HK.xlsx
+++ b/backend/data/financials_by_company/0176.HK.xlsx
@@ -3180,192 +3180,192 @@
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>priceToBook</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>longName</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>priceToBook</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
         </is>
       </c>
       <c r="EL1" t="inlineStr">
@@ -3498,7 +3498,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="AF2" t="n">
         <v>110000</v>
@@ -3628,7 +3628,7 @@
         <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="BV2" t="n">
         <v>0.005</v>
@@ -3738,142 +3738,142 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CZ2" t="n">
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DB2" t="n">
         <v>1743408508</v>
       </c>
-      <c r="DA2" t="inlineStr">
+      <c r="DC2" t="inlineStr">
         <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DD2" t="inlineStr">
         <is>
           <t>finmb_418667</t>
         </is>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DE2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DF2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DE2" t="n">
+      <c r="DG2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DH2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="DG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI2" t="n">
+      <c r="DI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK2" t="n">
         <v>0.013</v>
       </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DK2" t="b">
-        <v>0</v>
-      </c>
       <c r="DL2" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-0.8666667</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DT2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
         <v>946949400000</v>
       </c>
-      <c r="DM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN2" t="inlineStr">
+      <c r="DW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX2" t="inlineStr">
         <is>
           <t>0.013 - 0.015</t>
         </is>
       </c>
-      <c r="DO2" t="inlineStr">
+      <c r="DY2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS2" t="inlineStr">
+      <c r="DZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC2" t="inlineStr">
         <is>
           <t>0.013 - 0.015</t>
         </is>
       </c>
-      <c r="DT2" t="n">
+      <c r="ED2" t="n">
         <v>-0.0019999994</v>
       </c>
-      <c r="DU2" t="n">
+      <c r="EE2" t="n">
         <v>-0.1333333</v>
       </c>
-      <c r="DV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW2" t="n">
+      <c r="EF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG2" t="n">
         <v>1724845862</v>
       </c>
-      <c r="DX2" t="n">
+      <c r="EH2" t="n">
         <v>1724845862</v>
       </c>
-      <c r="DY2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="EA2" t="inlineStr">
+      <c r="EI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EJ2" t="inlineStr">
         <is>
           <t>SUPERACTIVE GP</t>
         </is>
       </c>
-      <c r="EB2" t="inlineStr">
+      <c r="EK2" t="inlineStr">
         <is>
           <t>Superactive Group Company Limited</t>
-        </is>
-      </c>
-      <c r="EC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>-0.8666667</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>[]</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr"/>
